--- a/packages/office-reader/src/spreadsheet/fixtures/incentivi.xlsx
+++ b/packages/office-reader/src/spreadsheet/fixtures/incentivi.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="https://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="https://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <sheets>
     <sheet name="Incentivi giugno" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="https://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Incentivi concessionari – giugno 2026</t>
   </si>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="https://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="https://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="https://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -254,7 +254,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="https://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -266,7 +266,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="https://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
